--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3866,1181 +3733,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天御第2期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>66 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>38 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>DUPLEX 46</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>DUPLEX 48</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>DUPLEX 50</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>PH52W</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>52&amp;53&amp;55/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>PH52W | 12582呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>B | 2727呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>50&amp;51/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>DUPLEX 50 | 8148呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
-      <c r="H9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>48&amp;49/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr"/>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>DUPLEX 48 | 8310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr"/>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr"/>
-      <c r="H11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>46&amp;47/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr"/>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>DUPLEX 46 | 8310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>- | 5591呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>- | 5593呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
-      <c r="H14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>- | 5577呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>- | 5577呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>- | 5577呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>- | 5470呎 (4+房)
-$42,291万
-$77,315/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>- | 5590呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr"/>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>- | 5590呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr"/>
-      <c r="H20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>- | 5483呎 (3房)
-$37,361万
-$68,140/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>A | 2727呎 (4+房)
-$16,133万
-$59,161/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$15,778万
-$57,945/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr"/>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>A | 2727呎 (4+房)
-$15,580万
-$57,132/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$16,469万
-$60,480/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>A | 2727呎 (4+房)
-$15,809万
-$57,971/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-$14,956万
-$53,933/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>A | 2727呎 (4+房)
-$15,410万
-$56,509/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$14,778万
-$54,271/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>A | 2727呎 (4+房)
-$15,071万
-$55,267/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$15,194万
-$55,798/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr"/>
-      <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$14,934万
-$54,985/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$14,415万
-$52,938/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr"/>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$13,694万
-$50,419/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$14,138万
-$51,921/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$13,583万
-$50,010/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$13,394万
-$49,187/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$14,155万
-$52,115/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$13,583万
-$49,883/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="16" t="inlineStr"/>
-      <c r="H30" s="16" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$14,150万
-$52,099/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$13,638万
-$50,084/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr"/>
-      <c r="G31" s="16" t="inlineStr"/>
-      <c r="H31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$13,272万
-$48,865/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$13,183万
-$48,413/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr"/>
-      <c r="F32" s="16" t="inlineStr"/>
-      <c r="G32" s="16" t="inlineStr"/>
-      <c r="H32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr"/>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$12,973万
-$47,765/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$14,162万
-$52,010/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr"/>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="16" t="inlineStr"/>
-      <c r="H33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$12,923万
-$47,581/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$12,859万
-$47,223/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr"/>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr"/>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="H35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr"/>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="H36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr"/>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="H37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr"/>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr"/>
-      <c r="F38" s="16" t="inlineStr"/>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="H38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="16" t="inlineStr"/>
-      <c r="H39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr"/>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr"/>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="H40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr"/>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr"/>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="16" t="inlineStr"/>
-      <c r="H41" s="16" t="inlineStr"/>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr"/>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr"/>
-      <c r="F42" s="16" t="inlineStr"/>
-      <c r="G42" s="16" t="inlineStr"/>
-      <c r="H42" s="16" t="inlineStr"/>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr"/>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr"/>
-      <c r="G43" s="16" t="inlineStr"/>
-      <c r="H43" s="16" t="inlineStr"/>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr"/>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr"/>
-      <c r="F44" s="16" t="inlineStr"/>
-      <c r="G44" s="16" t="inlineStr"/>
-      <c r="H44" s="16" t="inlineStr"/>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr"/>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr"/>
-      <c r="G45" s="16" t="inlineStr"/>
-      <c r="H45" s="16" t="inlineStr"/>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr"/>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>A | 2682呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>B | 2684呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr"/>
-      <c r="F46" s="16" t="inlineStr"/>
-      <c r="G46" s="16" t="inlineStr"/>
-      <c r="H46" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3733,4 +3903,1181 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>DUPLEX 46</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>DUPLEX 48</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>DUPLEX 50</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>PH52W</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>52&amp;53&amp;55</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>PH52W | 12582呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2727呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>50&amp;51</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>DUPLEX 50 | 8148呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>48&amp;49</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>DUPLEX 48 | 8310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>46&amp;47</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>DUPLEX 46 | 8310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>- | 5591呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>- | 5593呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>- | 5577呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>- | 5577呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>- | 5577呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>- | 5470呎 (4+房)
+$42291万
+$77,315/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>- | 5590呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>- | 5590呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>- | 5483呎 (3房)
+$37361万
+$68,140/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>A | 2727呎 (4+房)
+$16133万
+$59,161/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$15778万
+$57,945/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>A | 2727呎 (4+房)
+$15580万
+$57,132/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$16469万
+$60,480/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>A | 2727呎 (4+房)
+$15809万
+$57,971/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$14956万
+$53,933/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr"/>
+      <c r="H23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>A | 2727呎 (4+房)
+$15410万
+$56,509/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$14778万
+$54,271/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>A | 2727呎 (4+房)
+$15071万
+$55,267/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$15194万
+$55,798/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$14934万
+$54,985/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$14415万
+$52,938/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="inlineStr"/>
+      <c r="H26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$13694万
+$50,419/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$14138万
+$51,921/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$13583万
+$50,010/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$13394万
+$49,187/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$14155万
+$52,115/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$13583万
+$49,883/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
+      <c r="G29" s="20" t="inlineStr"/>
+      <c r="H29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$14150万
+$52,099/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$13638万
+$50,084/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$13272万
+$48,865/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$13183万
+$48,413/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$12973万
+$47,765/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$14162万
+$52,010/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="inlineStr"/>
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$12923万
+$47,581/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$12859万
+$47,223/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr"/>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr"/>
+      <c r="F41" s="20" t="inlineStr"/>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
+      <c r="G42" s="20" t="inlineStr"/>
+      <c r="H42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
+      <c r="G43" s="20" t="inlineStr"/>
+      <c r="H43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
+      <c r="G44" s="20" t="inlineStr"/>
+      <c r="H44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr"/>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>A | 2682呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>B | 2684呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr"/>
+      <c r="F45" s="20" t="inlineStr"/>
+      <c r="G45" s="20" t="inlineStr"/>
+      <c r="H45" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -754,6 +778,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -804,6 +848,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -854,6 +918,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -904,6 +988,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -954,6 +1058,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1004,6 +1128,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1054,6 +1198,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1104,6 +1268,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1154,6 +1338,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1204,6 +1408,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1254,6 +1478,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1304,6 +1548,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1350,6 +1614,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1400,6 +1684,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1450,6 +1754,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1496,6 +1820,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1542,6 +1886,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1588,6 +1952,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1634,6 +2018,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1680,6 +2084,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1726,6 +2150,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1772,6 +2216,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1818,6 +2282,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1864,6 +2348,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1910,6 +2414,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1956,6 +2480,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2002,6 +2546,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2048,6 +2612,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2094,6 +2678,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2140,6 +2744,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2186,6 +2810,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2232,6 +2876,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2278,6 +2942,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2324,6 +3008,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2370,6 +3074,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2416,6 +3140,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2462,6 +3206,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2508,6 +3272,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2554,6 +3338,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2600,6 +3404,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2646,6 +3470,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2692,6 +3536,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2742,6 +3606,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2792,6 +3676,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2842,6 +3746,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2892,6 +3816,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2942,6 +3886,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2992,6 +3956,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3042,6 +4026,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3092,6 +4096,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3142,6 +4166,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3192,6 +4236,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3242,6 +4306,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3292,6 +4376,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3342,6 +4446,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3392,6 +4516,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3442,6 +4586,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3492,6 +4656,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3542,6 +4726,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3592,6 +4796,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3642,6 +4866,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3692,6 +4936,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3742,6 +5006,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3792,6 +5076,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3842,6 +5146,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3892,13 +5216,33 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4300,7 +5644,7 @@
           <t>- | 5470呎 (4+房)
 $42291万
 $77,315/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -4363,7 +5707,7 @@
           <t>- | 5483呎 (3房)
 $37361万
 $68,140/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -4385,7 +5729,7 @@
           <t>A | 2727呎 (4+房)
 $16133万
 $59,161/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -4393,7 +5737,7 @@
           <t>B | 2723呎 (4+房)
 $15778万
 $57,945/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -4413,7 +5757,7 @@
           <t>A | 2727呎 (4+房)
 $15580万
 $57,132/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -4421,7 +5765,7 @@
           <t>B | 2723呎 (4+房)
 $16469万
 $60,480/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -4441,7 +5785,7 @@
           <t>A | 2727呎 (4+房)
 $15809万
 $57,971/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -4449,7 +5793,7 @@
           <t>B | 2773呎 (4+房)
 $14956万
 $53,933/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -4469,7 +5813,7 @@
           <t>A | 2727呎 (4+房)
 $15410万
 $56,509/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -4477,7 +5821,7 @@
           <t>B | 2723呎 (4+房)
 $14778万
 $54,271/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -4497,7 +5841,7 @@
           <t>A | 2727呎 (4+房)
 $15071万
 $55,267/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -4505,7 +5849,7 @@
           <t>B | 2723呎 (4+房)
 $15194万
 $55,798/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
@@ -4525,7 +5869,7 @@
           <t>A | 2716呎 (4+房)
 $14934万
 $54,985/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -4533,7 +5877,7 @@
           <t>B | 2723呎 (4+房)
 $14415万
 $52,938/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
@@ -4553,7 +5897,7 @@
           <t>A | 2716呎 (4+房)
 $13694万
 $50,419/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -4561,7 +5905,7 @@
           <t>B | 2723呎 (4+房)
 $14138万
 $51,921/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
@@ -4581,7 +5925,7 @@
           <t>A | 2716呎 (4+房)
 $13583万
 $50,010/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -4589,7 +5933,7 @@
           <t>B | 2723呎 (4+房)
 $13394万
 $49,187/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr"/>
@@ -4609,7 +5953,7 @@
           <t>A | 2716呎 (4+房)
 $14155万
 $52,115/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -4617,7 +5961,7 @@
           <t>B | 2723呎 (4+房)
 $13583万
 $49,883/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr"/>
@@ -4637,7 +5981,7 @@
           <t>A | 2716呎 (4+房)
 $14150万
 $52,099/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -4645,7 +5989,7 @@
           <t>B | 2723呎 (4+房)
 $13638万
 $50,084/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr"/>
@@ -4665,7 +6009,7 @@
           <t>A | 2716呎 (4+房)
 $13272万
 $48,865/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -4673,7 +6017,7 @@
           <t>B | 2723呎 (4+房)
 $13183万
 $48,413/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr"/>
@@ -4693,7 +6037,7 @@
           <t>A | 2716呎 (4+房)
 $12973万
 $47,765/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -4701,7 +6045,7 @@
           <t>B | 2723呎 (4+房)
 $14162万
 $52,010/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr"/>
@@ -4721,7 +6065,7 @@
           <t>A | 2716呎 (4+房)
 $12923万
 $47,581/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -4729,7 +6073,7 @@
           <t>B | 2723呎 (4+房)
 $12859万
 $47,223/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr"/>

--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -5644,7 +5644,7 @@
           <t>- | 5470呎 (4+房)
 $42291万
 $77,315/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -5707,7 +5707,7 @@
           <t>- | 5483呎 (3房)
 $37361万
 $68,140/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
           <t>A | 2727呎 (4+房)
 $16133万
 $59,161/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5737,7 +5737,7 @@
           <t>B | 2723呎 (4+房)
 $15778万
 $57,945/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
           <t>A | 2727呎 (4+房)
 $15580万
 $57,132/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5765,7 +5765,7 @@
           <t>B | 2723呎 (4+房)
 $16469万
 $60,480/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -5785,7 +5785,7 @@
           <t>A | 2727呎 (4+房)
 $15809万
 $57,971/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5793,7 +5793,7 @@
           <t>B | 2773呎 (4+房)
 $14956万
 $53,933/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -5813,7 +5813,7 @@
           <t>A | 2727呎 (4+房)
 $15410万
 $56,509/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -5821,7 +5821,7 @@
           <t>B | 2723呎 (4+房)
 $14778万
 $54,271/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
           <t>A | 2727呎 (4+房)
 $15071万
 $55,267/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5849,7 +5849,7 @@
           <t>B | 2723呎 (4+房)
 $15194万
 $55,798/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
@@ -5869,7 +5869,7 @@
           <t>A | 2716呎 (4+房)
 $14934万
 $54,985/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5877,7 +5877,7 @@
           <t>B | 2723呎 (4+房)
 $14415万
 $52,938/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
           <t>A | 2716呎 (4+房)
 $13694万
 $50,419/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5905,7 +5905,7 @@
           <t>B | 2723呎 (4+房)
 $14138万
 $51,921/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
           <t>A | 2716呎 (4+房)
 $13583万
 $50,010/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>B | 2723呎 (4+房)
 $13394万
 $49,187/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
           <t>A | 2716呎 (4+房)
 $14155万
 $52,115/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -5961,7 +5961,7 @@
           <t>B | 2723呎 (4+房)
 $13583万
 $49,883/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr"/>
@@ -5981,7 +5981,7 @@
           <t>A | 2716呎 (4+房)
 $14150万
 $52,099/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -5989,7 +5989,7 @@
           <t>B | 2723呎 (4+房)
 $13638万
 $50,084/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
           <t>A | 2716呎 (4+房)
 $13272万
 $48,865/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -6017,7 +6017,7 @@
           <t>B | 2723呎 (4+房)
 $13183万
 $48,413/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr"/>
@@ -6037,7 +6037,7 @@
           <t>A | 2716呎 (4+房)
 $12973万
 $47,765/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -6045,7 +6045,7 @@
           <t>B | 2723呎 (4+房)
 $14162万
 $52,010/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
           <t>A | 2716呎 (4+房)
 $12923万
 $47,581/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -6073,7 +6073,7 @@
           <t>B | 2723呎 (4+房)
 $12859万
 $47,223/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr"/>

--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -5644,7 +5644,7 @@
           <t>- | 5470呎 (4+房)
 $42291万
 $77,315/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -5707,7 +5707,7 @@
           <t>- | 5483呎 (3房)
 $37361万
 $68,140/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
           <t>A | 2727呎 (4+房)
 $16133万
 $59,161/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5737,7 +5737,7 @@
           <t>B | 2723呎 (4+房)
 $15778万
 $57,945/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
           <t>A | 2727呎 (4+房)
 $15580万
 $57,132/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5765,7 +5765,7 @@
           <t>B | 2723呎 (4+房)
 $16469万
 $60,480/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -5785,7 +5785,7 @@
           <t>A | 2727呎 (4+房)
 $15809万
 $57,971/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5793,7 +5793,7 @@
           <t>B | 2773呎 (4+房)
 $14956万
 $53,933/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -5813,7 +5813,7 @@
           <t>A | 2727呎 (4+房)
 $15410万
 $56,509/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -5821,7 +5821,7 @@
           <t>B | 2723呎 (4+房)
 $14778万
 $54,271/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
           <t>A | 2727呎 (4+房)
 $15071万
 $55,267/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5849,7 +5849,7 @@
           <t>B | 2723呎 (4+房)
 $15194万
 $55,798/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
@@ -5869,7 +5869,7 @@
           <t>A | 2716呎 (4+房)
 $14934万
 $54,985/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5877,7 +5877,7 @@
           <t>B | 2723呎 (4+房)
 $14415万
 $52,938/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
           <t>A | 2716呎 (4+房)
 $13694万
 $50,419/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5905,7 +5905,7 @@
           <t>B | 2723呎 (4+房)
 $14138万
 $51,921/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
@@ -5925,7 +5925,7 @@
           <t>A | 2716呎 (4+房)
 $13583万
 $50,010/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>B | 2723呎 (4+房)
 $13394万
 $49,187/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
           <t>A | 2716呎 (4+房)
 $14155万
 $52,115/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -5961,7 +5961,7 @@
           <t>B | 2723呎 (4+房)
 $13583万
 $49,883/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr"/>
@@ -5981,7 +5981,7 @@
           <t>A | 2716呎 (4+房)
 $14150万
 $52,099/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -5989,7 +5989,7 @@
           <t>B | 2723呎 (4+房)
 $13638万
 $50,084/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
           <t>A | 2716呎 (4+房)
 $13272万
 $48,865/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -6017,7 +6017,7 @@
           <t>B | 2723呎 (4+房)
 $13183万
 $48,413/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr"/>
@@ -6037,7 +6037,7 @@
           <t>A | 2716呎 (4+房)
 $12973万
 $47,765/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -6045,7 +6045,7 @@
           <t>B | 2723呎 (4+房)
 $14162万
 $52,010/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
           <t>A | 2716呎 (4+房)
 $12923万
 $47,581/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -6073,7 +6073,7 @@
           <t>B | 2723呎 (4+房)
 $12859万
 $47,223/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr"/>

--- a/files/港岛-半山区西部-天御第2期.xlsx
+++ b/files/港岛-半山区西部-天御第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,11 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +272,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1734,7 +1742,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1744,12 +1752,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1759,12 +1767,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1774,7 +1782,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5328,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -5681,12 +5689,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>- | 5590呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
